--- a/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Genus_by_Sample_Layer.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Genus_by_Sample_Layer.xlsx
@@ -872,10 +872,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>21.593320612441</v>
+        <v>21.6004891333318</v>
       </c>
       <c r="D2" t="n">
-        <v>1.21283305713485</v>
+        <v>1.21342084119697</v>
       </c>
     </row>
     <row r="3">
@@ -886,10 +886,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>17.4383623802787</v>
+        <v>17.4335608237773</v>
       </c>
       <c r="D3" t="n">
-        <v>0.57404082297464</v>
+        <v>0.573903827456795</v>
       </c>
     </row>
     <row r="4">
@@ -900,10 +900,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>15.6285124441035</v>
+        <v>15.6252452039893</v>
       </c>
       <c r="D4" t="n">
-        <v>2.15971300523427</v>
+        <v>2.15930845022779</v>
       </c>
     </row>
     <row r="5">
@@ -914,10 +914,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>8.36211780916747</v>
+        <v>8.36354044156639</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8880237394107</v>
+        <v>1.88837296899669</v>
       </c>
     </row>
     <row r="6">
@@ -928,7 +928,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>6.0952094129783</v>
+        <v>6.09481794786706</v>
       </c>
       <c r="D6"/>
     </row>
@@ -940,10 +940,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>3.90500227376959</v>
+        <v>3.90422965362823</v>
       </c>
       <c r="D7" t="n">
-        <v>0.266626492270157</v>
+        <v>0.266549307914427</v>
       </c>
     </row>
     <row r="8">
@@ -954,10 +954,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>3.22608947813918</v>
+        <v>3.22543327786321</v>
       </c>
       <c r="D8" t="n">
-        <v>0.652462783436685</v>
+        <v>0.65231206138855</v>
       </c>
     </row>
     <row r="9">
@@ -968,10 +968,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>3.01934852754756</v>
+        <v>3.02049654283758</v>
       </c>
       <c r="D9" t="n">
-        <v>0.739625173122029</v>
+        <v>0.739908294415527</v>
       </c>
     </row>
     <row r="10">
@@ -982,10 +982,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2.61567542300022</v>
+        <v>2.61572166037823</v>
       </c>
       <c r="D10" t="n">
-        <v>0.266309172716062</v>
+        <v>0.266328161330401</v>
       </c>
     </row>
     <row r="11">
@@ -996,10 +996,10 @@
         <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>2.12221346618614</v>
+        <v>2.12151181288669</v>
       </c>
       <c r="D11" t="n">
-        <v>0.588657670421057</v>
+        <v>0.588465550326627</v>
       </c>
     </row>
     <row r="12">
@@ -1010,7 +1010,7 @@
         <v>38</v>
       </c>
       <c r="C12" t="n">
-        <v>2.06154741135949</v>
+        <v>2.06235109116948</v>
       </c>
       <c r="D12"/>
     </row>
@@ -1022,10 +1022,10 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7609715488871</v>
+        <v>1.76041703797885</v>
       </c>
       <c r="D13" t="n">
-        <v>0.309479243177501</v>
+        <v>0.309379059161059</v>
       </c>
     </row>
     <row r="14">
@@ -1036,10 +1036,10 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>1.72372903290371</v>
+        <v>1.72346055486539</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0811177032377772</v>
+        <v>0.0811025054272378</v>
       </c>
     </row>
     <row r="15">
@@ -1050,10 +1050,10 @@
         <v>29</v>
       </c>
       <c r="C15" t="n">
-        <v>1.70582259717671</v>
+        <v>1.706495611628</v>
       </c>
       <c r="D15" t="n">
-        <v>1.05390239534565</v>
+        <v>1.05430225827595</v>
       </c>
     </row>
     <row r="16">
@@ -1064,10 +1064,10 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>1.27604330034489</v>
+        <v>1.27570358577485</v>
       </c>
       <c r="D16" t="n">
-        <v>0.286174586870707</v>
+        <v>0.286113399427014</v>
       </c>
     </row>
     <row r="17">
@@ -1078,10 +1078,10 @@
         <v>49</v>
       </c>
       <c r="C17" t="n">
-        <v>0.98483464546458</v>
+        <v>0.984493672178256</v>
       </c>
       <c r="D17" t="n">
-        <v>0.41693837682382</v>
+        <v>0.416794022795259</v>
       </c>
     </row>
     <row r="18">
@@ -1092,10 +1092,10 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>0.749567042642019</v>
+        <v>0.749740683848614</v>
       </c>
       <c r="D18" t="n">
-        <v>0.194544793301194</v>
+        <v>0.194610471514287</v>
       </c>
     </row>
     <row r="19">
@@ -1106,7 +1106,7 @@
         <v>71</v>
       </c>
       <c r="C19" t="n">
-        <v>0.655033868085706</v>
+        <v>0.655082977305879</v>
       </c>
       <c r="D19"/>
     </row>
@@ -1118,10 +1118,10 @@
         <v>55</v>
       </c>
       <c r="C20" t="n">
-        <v>0.575423643279072</v>
+        <v>0.575654818115614</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0615288647184127</v>
+        <v>0.061570583041011</v>
       </c>
     </row>
     <row r="21">
@@ -1132,10 +1132,10 @@
         <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>0.564474994923797</v>
+        <v>0.564279560192745</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0340832466395912</v>
+        <v>0.0340714462052048</v>
       </c>
     </row>
     <row r="22">
@@ -1146,10 +1146,10 @@
         <v>74</v>
       </c>
       <c r="C22" t="n">
-        <v>0.476568415956346</v>
+        <v>0.476687591108285</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1140976927596</v>
+        <v>0.114127320086749</v>
       </c>
     </row>
     <row r="23">
@@ -1160,7 +1160,7 @@
         <v>17</v>
       </c>
       <c r="C23" t="n">
-        <v>0.374544787244193</v>
+        <v>0.374492362216465</v>
       </c>
       <c r="D23"/>
     </row>
@@ -1172,10 +1172,10 @@
         <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>0.346145091863355</v>
+        <v>0.346314940638425</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0399684363248702</v>
+        <v>0.0399880491030856</v>
       </c>
     </row>
     <row r="25">
@@ -1186,7 +1186,7 @@
         <v>30</v>
       </c>
       <c r="C25" t="n">
-        <v>0.330421761971748</v>
+        <v>0.330467382668754</v>
       </c>
       <c r="D25"/>
     </row>
@@ -1198,10 +1198,10 @@
         <v>67</v>
       </c>
       <c r="C26" t="n">
-        <v>0.267395965692175</v>
+        <v>0.26736132531494</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0389345544674118</v>
+        <v>0.0389228832239507</v>
       </c>
     </row>
     <row r="27">
@@ -1212,10 +1212,10 @@
         <v>77</v>
       </c>
       <c r="C27" t="n">
-        <v>0.260992924556748</v>
+        <v>0.26104878829638</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00543901526738068</v>
+        <v>0.00544298482218474</v>
       </c>
     </row>
     <row r="28">
@@ -1226,7 +1226,7 @@
         <v>22</v>
       </c>
       <c r="C28" t="n">
-        <v>0.215379536261402</v>
+        <v>0.215484300157604</v>
       </c>
       <c r="D28"/>
     </row>
@@ -1238,7 +1238,7 @@
         <v>53</v>
       </c>
       <c r="C29" t="n">
-        <v>0.199995677947234</v>
+        <v>0.200091973222925</v>
       </c>
       <c r="D29"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>31</v>
       </c>
       <c r="C30" t="n">
-        <v>0.198168603278418</v>
+        <v>0.198099992572837</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0102348477225202</v>
+        <v>0.0102313041736828</v>
       </c>
     </row>
     <row r="31">
@@ -1264,10 +1264,10 @@
         <v>86</v>
       </c>
       <c r="C31" t="n">
-        <v>0.190073724118846</v>
+        <v>0.190090685332942</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00701588083467295</v>
+        <v>0.00707197848760562</v>
       </c>
     </row>
     <row r="32">
@@ -1278,7 +1278,7 @@
         <v>65</v>
       </c>
       <c r="C32" t="n">
-        <v>0.169225201387374</v>
+        <v>0.169310078329535</v>
       </c>
       <c r="D32"/>
     </row>
@@ -1290,7 +1290,7 @@
         <v>68</v>
       </c>
       <c r="C33" t="n">
-        <v>0.16153327223029</v>
+        <v>0.161612535374211</v>
       </c>
       <c r="D33"/>
     </row>
@@ -1302,7 +1302,7 @@
         <v>39</v>
       </c>
       <c r="C34" t="n">
-        <v>0.15404281807445</v>
+        <v>0.154072254049156</v>
       </c>
       <c r="D34"/>
     </row>
@@ -1314,10 +1314,10 @@
         <v>23</v>
       </c>
       <c r="C35" t="n">
-        <v>0.150868896821975</v>
+        <v>0.150844252164665</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0156795106512313</v>
+        <v>0.0156700114403627</v>
       </c>
     </row>
     <row r="36">
@@ -1328,7 +1328,7 @@
         <v>78</v>
       </c>
       <c r="C36" t="n">
-        <v>0.132112402185612</v>
+        <v>0.132066661715225</v>
       </c>
       <c r="D36"/>
     </row>
@@ -1340,7 +1340,7 @@
         <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>0.125162894608455</v>
+        <v>0.125138873055433</v>
       </c>
       <c r="D37"/>
     </row>
@@ -1352,10 +1352,10 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0889305135628142</v>
+        <v>0.0889659391173463</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0193712470556227</v>
+        <v>0.0193723438294962</v>
       </c>
     </row>
     <row r="39">
@@ -1366,7 +1366,7 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0300252950484096</v>
+        <v>0.0300148995738265</v>
       </c>
       <c r="D39"/>
     </row>
@@ -1378,7 +1378,7 @@
         <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0300252950484096</v>
+        <v>0.0300148995738265</v>
       </c>
       <c r="D40"/>
     </row>
@@ -1390,7 +1390,7 @@
         <v>89</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0230757874712522</v>
+        <v>0.0230871109140344</v>
       </c>
       <c r="D41"/>
     </row>
@@ -1402,7 +1402,7 @@
         <v>92</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0120112219919734</v>
+        <v>0.0120070634199185</v>
       </c>
       <c r="D42"/>
     </row>
@@ -1439,10 +1439,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>19.4125027455314</v>
+        <v>19.4115818953403</v>
       </c>
       <c r="D2" t="n">
-        <v>1.41594364500501</v>
+        <v>1.4157656383204</v>
       </c>
     </row>
     <row r="3">
@@ -1453,10 +1453,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>18.7585675464447</v>
+        <v>18.7596754229218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.445227623743765</v>
+        <v>0.445256521377909</v>
       </c>
     </row>
     <row r="4">
@@ -1467,10 +1467,10 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>15.4088131875933</v>
+        <v>15.4088719795948</v>
       </c>
       <c r="D4" t="n">
-        <v>10.7345361992899</v>
+        <v>10.7344944659556</v>
       </c>
     </row>
     <row r="5">
@@ -1481,10 +1481,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>8.27218139624052</v>
+        <v>8.27101045526418</v>
       </c>
       <c r="D5" t="n">
-        <v>1.36968109620548</v>
+        <v>1.36954730085311</v>
       </c>
     </row>
     <row r="6">
@@ -1495,10 +1495,10 @@
         <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>5.75200313986558</v>
+        <v>5.75290790518388</v>
       </c>
       <c r="D6" t="n">
-        <v>1.01899653575214</v>
+        <v>1.01917258605361</v>
       </c>
     </row>
     <row r="7">
@@ -1509,10 +1509,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>5.50235662250732</v>
+        <v>5.50252043016617</v>
       </c>
       <c r="D7" t="n">
-        <v>0.800444125543568</v>
+        <v>0.80046181295353</v>
       </c>
     </row>
     <row r="8">
@@ -1523,10 +1523,10 @@
         <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>4.01645242788765</v>
+        <v>4.01579072395459</v>
       </c>
       <c r="D8" t="n">
-        <v>1.90474767622298</v>
+        <v>1.90442337340355</v>
       </c>
     </row>
     <row r="9">
@@ -1537,10 +1537,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>3.79181291948954</v>
+        <v>3.79180493338407</v>
       </c>
       <c r="D9" t="n">
-        <v>0.523518167184392</v>
+        <v>0.523491402329329</v>
       </c>
     </row>
     <row r="10">
@@ -1551,10 +1551,10 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>3.03219354452458</v>
+        <v>3.03231087200026</v>
       </c>
       <c r="D10" t="n">
-        <v>0.125337392344294</v>
+        <v>0.12535609475634</v>
       </c>
     </row>
     <row r="11">
@@ -1565,10 +1565,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>2.81823734043234</v>
+        <v>2.81821542032565</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0376989629613186</v>
+        <v>0.0376965176025091</v>
       </c>
     </row>
     <row r="12">
@@ -1579,10 +1579,10 @@
         <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>2.68256657067358</v>
+        <v>2.68243549456141</v>
       </c>
       <c r="D12" t="n">
-        <v>0.121381233006726</v>
+        <v>0.121368390366091</v>
       </c>
     </row>
     <row r="13">
@@ -1593,10 +1593,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>2.03818901815036</v>
+        <v>2.03841763438147</v>
       </c>
       <c r="D13" t="n">
-        <v>0.075051386182861</v>
+        <v>0.0750640111323821</v>
       </c>
     </row>
     <row r="14">
@@ -1607,10 +1607,10 @@
         <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>1.73603927064758</v>
+        <v>1.73634246894241</v>
       </c>
       <c r="D14" t="n">
-        <v>0.137986526107818</v>
+        <v>0.138006835212184</v>
       </c>
     </row>
     <row r="15">
@@ -1621,10 +1621,10 @@
         <v>34</v>
       </c>
       <c r="C15" t="n">
-        <v>1.58574655495638</v>
+        <v>1.5857200763407</v>
       </c>
       <c r="D15" t="n">
-        <v>0.149916665967348</v>
+        <v>0.149933979851808</v>
       </c>
     </row>
     <row r="16">
@@ -1635,10 +1635,10 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>1.10727470705888</v>
+        <v>1.10696295978783</v>
       </c>
       <c r="D16" t="n">
-        <v>0.554741443716215</v>
+        <v>0.554561864968259</v>
       </c>
     </row>
     <row r="17">
@@ -1649,10 +1649,10 @@
         <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>0.619273063923512</v>
+        <v>0.619285054446558</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0899272762099066</v>
+        <v>0.0899205899723074</v>
       </c>
     </row>
     <row r="18">
@@ -1663,10 +1663,10 @@
         <v>31</v>
       </c>
       <c r="C18" t="n">
-        <v>0.533191579369875</v>
+        <v>0.533244440897158</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0473778828666499</v>
+        <v>0.0473843566599068</v>
       </c>
     </row>
     <row r="19">
@@ -1677,10 +1677,10 @@
         <v>38</v>
       </c>
       <c r="C19" t="n">
-        <v>0.421336013930581</v>
+        <v>0.421468998536732</v>
       </c>
       <c r="D19" t="n">
-        <v>0.208063181703773</v>
+        <v>0.208111513998807</v>
       </c>
     </row>
     <row r="20">
@@ -1691,10 +1691,10 @@
         <v>81</v>
       </c>
       <c r="C20" t="n">
-        <v>0.335446007240345</v>
+        <v>0.335502608919009</v>
       </c>
       <c r="D20" t="n">
-        <v>0.145391150819068</v>
+        <v>0.145399331381891</v>
       </c>
     </row>
     <row r="21">
@@ -1705,10 +1705,10 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>0.327482849066667</v>
+        <v>0.327415679613048</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0352004257476803</v>
+        <v>0.035190434385075</v>
       </c>
     </row>
     <row r="22">
@@ -1719,10 +1719,10 @@
         <v>86</v>
       </c>
       <c r="C22" t="n">
-        <v>0.314411293591834</v>
+        <v>0.31444156830575</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0797749082016171</v>
+        <v>0.0797227487189153</v>
       </c>
     </row>
     <row r="23">
@@ -1733,10 +1733,10 @@
         <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>0.313011764481159</v>
+        <v>0.313003479629514</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0264669082796906</v>
+        <v>0.0264561600207882</v>
       </c>
     </row>
     <row r="24">
@@ -1747,10 +1747,10 @@
         <v>37</v>
       </c>
       <c r="C24" t="n">
-        <v>0.253850907049785</v>
+        <v>0.253812213615222</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07776340641984</v>
+        <v>0.0777507059732587</v>
       </c>
     </row>
     <row r="25">
@@ -1761,10 +1761,10 @@
         <v>25</v>
       </c>
       <c r="C25" t="n">
-        <v>0.247608728702917</v>
+        <v>0.247735129209194</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0422823286117328</v>
+        <v>0.0423031580187295</v>
       </c>
     </row>
     <row r="26">
@@ -1775,7 +1775,7 @@
         <v>78</v>
       </c>
       <c r="C26" t="n">
-        <v>0.152865481892164</v>
+        <v>0.152889701764647</v>
       </c>
       <c r="D26"/>
     </row>
@@ -1787,7 +1787,7 @@
         <v>42</v>
       </c>
       <c r="C27" t="n">
-        <v>0.152516179850445</v>
+        <v>0.152530179595588</v>
       </c>
       <c r="D27"/>
     </row>
@@ -1799,10 +1799,10 @@
         <v>67</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0980842454091233</v>
+        <v>0.0980799672171447</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0230756382404663</v>
+        <v>0.0230733844377137</v>
       </c>
     </row>
     <row r="29">
@@ -1813,7 +1813,7 @@
         <v>71</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0693347145734065</v>
+        <v>0.0693286314328213</v>
       </c>
       <c r="D29"/>
     </row>
@@ -1825,7 +1825,7 @@
         <v>87</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0437381858883574</v>
+        <v>0.0437387712383516</v>
       </c>
       <c r="D30"/>
     </row>
@@ -1837,7 +1837,7 @@
         <v>90</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0405851837376897</v>
+        <v>0.0405772956484978</v>
       </c>
       <c r="D31"/>
     </row>
@@ -1849,10 +1849,10 @@
         <v>53</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0249814785783675</v>
+        <v>0.0249786725070694</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00217042761827313</v>
+        <v>0.00216005472535743</v>
       </c>
     </row>
     <row r="33">
@@ -1863,10 +1863,10 @@
         <v>39</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0241030013505223</v>
+        <v>0.024115819301328</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00154925041334581</v>
+        <v>0.00154992537240909</v>
       </c>
     </row>
     <row r="34">
@@ -1877,7 +1877,7 @@
         <v>48</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0219120304044565</v>
+        <v>0.0219238938190009</v>
       </c>
       <c r="D34"/>
     </row>
@@ -1889,7 +1889,7 @@
         <v>15</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0197210594583907</v>
+        <v>0.0197308085877413</v>
       </c>
       <c r="D35"/>
     </row>
@@ -1901,7 +1901,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0143747654178584</v>
+        <v>0.0143750880176955</v>
       </c>
       <c r="D36"/>
     </row>
@@ -1913,7 +1913,7 @@
         <v>22</v>
       </c>
       <c r="C37" t="n">
-        <v>0.013146986148294</v>
+        <v>0.0131538723918275</v>
       </c>
       <c r="D37"/>
     </row>
@@ -1925,10 +1925,10 @@
         <v>57</v>
       </c>
       <c r="C38" t="n">
-        <v>0.013146986148294</v>
+        <v>0.0131538723918275</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00309932140424106</v>
+        <v>0.00309985074481818</v>
       </c>
     </row>
     <row r="39">
@@ -1939,7 +1939,7 @@
         <v>92</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0112206027952913</v>
+        <v>0.0112136124278417</v>
       </c>
       <c r="D39"/>
     </row>
@@ -1951,7 +1951,7 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>0.00657407331009671</v>
+        <v>0.00657693619591377</v>
       </c>
       <c r="D40"/>
     </row>
@@ -1963,7 +1963,7 @@
         <v>41</v>
       </c>
       <c r="C41" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="D41"/>
     </row>
@@ -1975,7 +1975,7 @@
         <v>43</v>
       </c>
       <c r="C42" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="D42"/>
     </row>
@@ -1987,7 +1987,7 @@
         <v>47</v>
       </c>
       <c r="C43" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="D43"/>
     </row>
@@ -2603,10 +2603,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>24.631392707249</v>
+        <v>24.6310091422731</v>
       </c>
       <c r="D2" t="n">
-        <v>4.59419934557097</v>
+        <v>4.59411313201896</v>
       </c>
     </row>
     <row r="3">
@@ -2617,10 +2617,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>21.9561628285138</v>
+        <v>21.9557849726509</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16771398525829</v>
+        <v>1.16769782773181</v>
       </c>
     </row>
     <row r="4">
@@ -2631,10 +2631,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2655397706116</v>
+        <v>19.2658310749008</v>
       </c>
       <c r="D4" t="n">
-        <v>0.801037083083817</v>
+        <v>0.801053720061133</v>
       </c>
     </row>
     <row r="5">
@@ -2645,10 +2645,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>5.64193695488102</v>
+        <v>5.64180376429859</v>
       </c>
       <c r="D5" t="n">
-        <v>1.11225319868185</v>
+        <v>1.11217301857517</v>
       </c>
     </row>
     <row r="6">
@@ -2659,10 +2659,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>5.54204949466641</v>
+        <v>5.5422000955275</v>
       </c>
       <c r="D6" t="n">
-        <v>1.05968322937623</v>
+        <v>1.05970997848961</v>
       </c>
     </row>
     <row r="7">
@@ -2673,10 +2673,10 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>4.31468317592953</v>
+        <v>4.31466532273081</v>
       </c>
       <c r="D7" t="n">
-        <v>0.152549459352072</v>
+        <v>0.152541833505149</v>
       </c>
     </row>
     <row r="8">
@@ -2687,10 +2687,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>3.93840198783546</v>
+        <v>3.93853124820496</v>
       </c>
       <c r="D8" t="n">
-        <v>2.37820589277897</v>
+        <v>2.37830413975467</v>
       </c>
     </row>
     <row r="9">
@@ -2701,10 +2701,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>2.68983581567514</v>
+        <v>2.68972901058529</v>
       </c>
       <c r="D9" t="n">
-        <v>0.324633621661211</v>
+        <v>0.324586081290426</v>
       </c>
     </row>
     <row r="10">
@@ -2715,10 +2715,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>2.10025012562121</v>
+        <v>2.10056275535414</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0640374692467378</v>
+        <v>0.0640422498229953</v>
       </c>
     </row>
     <row r="11">
@@ -2729,10 +2729,10 @@
         <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>1.54109912852667</v>
+        <v>1.54123712106465</v>
       </c>
       <c r="D11" t="n">
-        <v>0.190189528807136</v>
+        <v>0.190209468161239</v>
       </c>
     </row>
     <row r="12">
@@ -2743,10 +2743,10 @@
         <v>81</v>
       </c>
       <c r="C12" t="n">
-        <v>1.14667551612367</v>
+        <v>1.1465334653637</v>
       </c>
       <c r="D12" t="n">
-        <v>0.369766800613695</v>
+        <v>0.36969012059224</v>
       </c>
     </row>
     <row r="13">
@@ -2757,10 +2757,10 @@
         <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>0.956395560811265</v>
+        <v>0.956500761814801</v>
       </c>
       <c r="D13" t="n">
-        <v>0.101961225414945</v>
+        <v>0.101967492441141</v>
       </c>
     </row>
     <row r="14">
@@ -2771,7 +2771,7 @@
         <v>92</v>
       </c>
       <c r="C14" t="n">
-        <v>0.82757160892989</v>
+        <v>0.827567995110726</v>
       </c>
       <c r="D14"/>
     </row>
@@ -2783,10 +2783,10 @@
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>0.74669543823414</v>
+        <v>0.74669857065911</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0292177805808028</v>
+        <v>0.0292161963875212</v>
       </c>
     </row>
     <row r="16">
@@ -2797,10 +2797,10 @@
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>0.70082866169531</v>
+        <v>0.700971005602779</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0239307351581613</v>
+        <v>0.0239368353304814</v>
       </c>
     </row>
     <row r="17">
@@ -2811,7 +2811,7 @@
         <v>95</v>
       </c>
       <c r="C17" t="n">
-        <v>0.561396773370258</v>
+        <v>0.561284058446422</v>
       </c>
       <c r="D17"/>
     </row>
@@ -2823,10 +2823,10 @@
         <v>49</v>
       </c>
       <c r="C18" t="n">
-        <v>0.509147384705421</v>
+        <v>0.509037052599851</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1146841955465</v>
+        <v>0.114665641911313</v>
       </c>
     </row>
     <row r="19">
@@ -2837,10 +2837,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>0.494233263792842</v>
+        <v>0.494234140852321</v>
       </c>
       <c r="D19" t="n">
-        <v>0.212731530238071</v>
+        <v>0.212728315557499</v>
       </c>
     </row>
     <row r="20">
@@ -2851,10 +2851,10 @@
         <v>34</v>
       </c>
       <c r="C20" t="n">
-        <v>0.407956245260099</v>
+        <v>0.407987245009878</v>
       </c>
       <c r="D20" t="n">
-        <v>0.04072813612845</v>
+        <v>0.0407363638337707</v>
       </c>
     </row>
     <row r="21">
@@ -2865,10 +2865,10 @@
         <v>86</v>
       </c>
       <c r="C21" t="n">
-        <v>0.357665045351981</v>
+        <v>0.357642250946709</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0489665019883578</v>
+        <v>0.0489714570978644</v>
       </c>
     </row>
     <row r="22">
@@ -2879,10 +2879,10 @@
         <v>42</v>
       </c>
       <c r="C22" t="n">
-        <v>0.249306340048411</v>
+        <v>0.249311435523764</v>
       </c>
       <c r="D22" t="n">
-        <v>0.026880090038289</v>
+        <v>0.0268774857163241</v>
       </c>
     </row>
     <row r="23">
@@ -2893,7 +2893,7 @@
         <v>41</v>
       </c>
       <c r="C23" t="n">
-        <v>0.222556886622985</v>
+        <v>0.22251479576491</v>
       </c>
       <c r="D23"/>
     </row>
@@ -2905,10 +2905,10 @@
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>0.195206321884627</v>
+        <v>0.19522340424356</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0113929895460777</v>
+        <v>0.0113938240662738</v>
       </c>
     </row>
     <row r="25">
@@ -2919,10 +2919,10 @@
         <v>65</v>
       </c>
       <c r="C25" t="n">
-        <v>0.092479602397516</v>
+        <v>0.0924987590230735</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0146116242967509</v>
+        <v>0.014618736694941</v>
       </c>
     </row>
     <row r="26">
@@ -2933,10 +2933,10 @@
         <v>39</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0867179352064407</v>
+        <v>0.0867218270412637</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03241140326452</v>
+        <v>0.0324165306828944</v>
       </c>
     </row>
     <row r="27">
@@ -2947,7 +2947,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0794954454718848</v>
+        <v>0.0794804603356408</v>
       </c>
       <c r="D27"/>
     </row>
@@ -2959,10 +2959,10 @@
         <v>23</v>
       </c>
       <c r="C28" t="n">
-        <v>0.074254792274124</v>
+        <v>0.0742539301604906</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0189524110839475</v>
+        <v>0.0189479555191827</v>
       </c>
     </row>
     <row r="29">
@@ -2973,10 +2973,10 @@
         <v>25</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0571780437319009</v>
+        <v>0.0571686042728791</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0088145416049972</v>
+        <v>0.00880422534147926</v>
       </c>
     </row>
     <row r="30">
@@ -2987,10 +2987,10 @@
         <v>15</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0542304623700162</v>
+        <v>0.0542595553889274</v>
       </c>
       <c r="D30" t="n">
-        <v>0.011559847004357</v>
+        <v>0.0115623328292755</v>
       </c>
     </row>
     <row r="31">
@@ -3001,10 +3001,10 @@
         <v>37</v>
       </c>
       <c r="C31" t="n">
-        <v>0.051623866740213</v>
+        <v>0.0516379046782591</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0104755880492871</v>
+        <v>0.0104789957127142</v>
       </c>
     </row>
     <row r="32">
@@ -3015,10 +3015,10 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0470087354670757</v>
+        <v>0.0470197133420486</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0132300081670565</v>
+        <v>0.0132324087357708</v>
       </c>
     </row>
     <row r="33">
@@ -3029,7 +3029,7 @@
         <v>45</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0461749605114494</v>
+        <v>0.046163617457175</v>
       </c>
       <c r="D33"/>
     </row>
@@ -3041,10 +3041,10 @@
         <v>38</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0389265345019701</v>
+        <v>0.0389413089858546</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0103389583512876</v>
+        <v>0.0103504220575672</v>
       </c>
     </row>
     <row r="35">
@@ -3055,7 +3055,7 @@
         <v>70</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0380134250583428</v>
+        <v>0.0380105048225147</v>
       </c>
       <c r="D35"/>
     </row>
@@ -3067,10 +3067,10 @@
         <v>44</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0330077239981236</v>
+        <v>0.033012673458996</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0187680021831362</v>
+        <v>0.0187745121440375</v>
       </c>
     </row>
     <row r="37">
@@ -3081,10 +3081,10 @@
         <v>22</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0319389969049558</v>
+        <v>0.0319286410918631</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0117066721670577</v>
+        <v>0.0116914178957773</v>
       </c>
     </row>
     <row r="38">
@@ -3095,7 +3095,7 @@
         <v>83</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0286275448625279</v>
+        <v>0.0286216562756727</v>
       </c>
       <c r="D38"/>
     </row>
@@ -3107,10 +3107,10 @@
         <v>59</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0282369750754459</v>
+        <v>0.0282420162483645</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00396353624307883</v>
+        <v>0.00397763717335705</v>
       </c>
     </row>
     <row r="40">
@@ -3121,7 +3121,7 @@
         <v>62</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0261506306073417</v>
+        <v>0.0261707673443559</v>
       </c>
       <c r="D40"/>
     </row>
@@ -3133,7 +3133,7 @@
         <v>87</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0215354993342044</v>
+        <v>0.0215518136787733</v>
       </c>
       <c r="D41"/>
     </row>
@@ -3145,10 +3145,10 @@
         <v>57</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0203103917598807</v>
+        <v>0.0203168400959636</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00385483829527122</v>
+        <v>0.00385801905830888</v>
       </c>
     </row>
     <row r="43">
@@ -3159,10 +3159,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0191638558419427</v>
+        <v>0.0191573371209923</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00702411118091624</v>
+        <v>0.00701517416642751</v>
       </c>
     </row>
     <row r="44">
@@ -3173,7 +3173,7 @@
         <v>29</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0169211308926826</v>
+        <v>0.0169336223425627</v>
       </c>
       <c r="D44"/>
     </row>
@@ -3185,10 +3185,10 @@
         <v>55</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0160080214490553</v>
+        <v>0.0160020558498507</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00446140558880036</v>
+        <v>0.00446170251848167</v>
       </c>
     </row>
     <row r="46">
@@ -3199,10 +3199,10 @@
         <v>74</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0140010114689522</v>
+        <v>0.0140070398830526</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00262057087127245</v>
+        <v>0.00262361767959266</v>
       </c>
     </row>
     <row r="47">
@@ -3213,7 +3213,7 @@
         <v>48</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0123059996195454</v>
+        <v>0.0123154310063522</v>
       </c>
       <c r="D47"/>
     </row>
@@ -3225,7 +3225,7 @@
         <v>97</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0107681310829099</v>
+        <v>0.0107762880040727</v>
       </c>
       <c r="D48"/>
     </row>
@@ -3237,7 +3237,7 @@
         <v>90</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0107681310829099</v>
+        <v>0.0107762880040727</v>
       </c>
       <c r="D49"/>
     </row>
@@ -3249,7 +3249,7 @@
         <v>98</v>
       </c>
       <c r="C50" t="n">
-        <v>0.00769163117802357</v>
+        <v>0.00769723967014162</v>
       </c>
       <c r="D50"/>
     </row>
@@ -3261,7 +3261,7 @@
         <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>0.00646576077208448</v>
+        <v>0.00646150375795982</v>
       </c>
       <c r="D51"/>
     </row>
@@ -3273,7 +3273,7 @@
         <v>99</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00646576077208448</v>
+        <v>0.00646150375795982</v>
       </c>
       <c r="D52"/>
     </row>
@@ -3285,7 +3285,7 @@
         <v>89</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00630938029092859</v>
+        <v>0.00630980021291098</v>
       </c>
       <c r="D53"/>
     </row>
@@ -3297,7 +3297,7 @@
         <v>66</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0061529998097727</v>
+        <v>0.00615809666786214</v>
       </c>
       <c r="D54"/>
     </row>
@@ -3309,7 +3309,7 @@
         <v>100</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00484932057906336</v>
+        <v>0.00484612781846987</v>
       </c>
       <c r="D55"/>
     </row>
@@ -3321,7 +3321,7 @@
         <v>52</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00461513127313722</v>
+        <v>0.00461819133621055</v>
       </c>
       <c r="D56"/>
     </row>
@@ -3333,7 +3333,7 @@
         <v>35</v>
       </c>
       <c r="C57" t="n">
-        <v>0.00461513127313722</v>
+        <v>0.00461819133621055</v>
       </c>
       <c r="D57"/>
     </row>
@@ -3370,10 +3370,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>19.8741580235539</v>
+        <v>19.8722980417864</v>
       </c>
       <c r="D2" t="n">
-        <v>1.08247297210186</v>
+        <v>1.08232234927472</v>
       </c>
     </row>
     <row r="3">
@@ -3384,10 +3384,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>17.7241798195007</v>
+        <v>17.7224537820169</v>
       </c>
       <c r="D3" t="n">
-        <v>4.54736451659128</v>
+        <v>4.54672531155237</v>
       </c>
     </row>
     <row r="4">
@@ -3398,10 +3398,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>12.5118933543116</v>
+        <v>12.5158221148857</v>
       </c>
       <c r="D4" t="n">
-        <v>4.84513813620268</v>
+        <v>4.84664378215444</v>
       </c>
     </row>
     <row r="5">
@@ -3412,10 +3412,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>10.6290535606668</v>
+        <v>10.6283808772554</v>
       </c>
       <c r="D5" t="n">
-        <v>5.72148293638644</v>
+        <v>5.72085521364488</v>
       </c>
     </row>
     <row r="6">
@@ -3426,10 +3426,10 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>9.39450066973325</v>
+        <v>9.39293921525338</v>
       </c>
       <c r="D6" t="n">
-        <v>1.66634977712536</v>
+        <v>1.6659702542067</v>
       </c>
     </row>
     <row r="7">
@@ -3440,10 +3440,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>6.00404627902126</v>
+        <v>6.00307210922042</v>
       </c>
       <c r="D7" t="n">
-        <v>1.24378836207599</v>
+        <v>1.24351144922079</v>
       </c>
     </row>
     <row r="8">
@@ -3454,10 +3454,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>5.84999160049945</v>
+        <v>5.84984507449901</v>
       </c>
       <c r="D8" t="n">
-        <v>0.802981898007005</v>
+        <v>0.802960025767448</v>
       </c>
     </row>
     <row r="9">
@@ -3468,7 +3468,7 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>5.12700882116796</v>
+        <v>5.12663012137111</v>
       </c>
       <c r="D9"/>
     </row>
@@ -3480,10 +3480,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4.5410657193669</v>
+        <v>4.54254025821407</v>
       </c>
       <c r="D10" t="n">
-        <v>1.26372211027965</v>
+        <v>1.26424553476954</v>
       </c>
     </row>
     <row r="11">
@@ -3494,10 +3494,10 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>3.42924529730402</v>
+        <v>3.4306325226418</v>
       </c>
       <c r="D11" t="n">
-        <v>1.30875082780457</v>
+        <v>1.30926703969254</v>
       </c>
     </row>
     <row r="12">
@@ -3508,10 +3508,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>1.21751116830729</v>
+        <v>1.2177090508129</v>
       </c>
       <c r="D12" t="n">
-        <v>0.489497778370004</v>
+        <v>0.489615016945174</v>
       </c>
     </row>
     <row r="13">
@@ -3522,10 +3522,10 @@
         <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>1.08354447878472</v>
+        <v>1.0837060721082</v>
       </c>
       <c r="D13" t="n">
-        <v>0.269216117329756</v>
+        <v>0.269245368434525</v>
       </c>
     </row>
     <row r="14">
@@ -3536,10 +3536,10 @@
         <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0764610187463</v>
+        <v>1.07669850745551</v>
       </c>
       <c r="D14" t="n">
-        <v>0.186974950143159</v>
+        <v>0.18702418051521</v>
       </c>
     </row>
     <row r="15">
@@ -3550,10 +3550,10 @@
         <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>0.776644275718104</v>
+        <v>0.776524088548015</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0412337211331349</v>
+        <v>0.0411156528901548</v>
       </c>
     </row>
     <row r="16">
@@ -3564,10 +3564,10 @@
         <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>0.272068552038335</v>
+        <v>0.272095187481516</v>
       </c>
       <c r="D16" t="n">
-        <v>0.112442581800846</v>
+        <v>0.112472967401727</v>
       </c>
     </row>
     <row r="17">
@@ -3578,7 +3578,7 @@
         <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.106510209713172</v>
+        <v>0.106529229357992</v>
       </c>
       <c r="D17"/>
     </row>
@@ -3590,10 +3590,10 @@
         <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>0.077869070758711</v>
+        <v>0.0778868105568116</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0128911473218381</v>
+        <v>0.0129181946812718</v>
       </c>
     </row>
     <row r="19">
@@ -3604,7 +3604,7 @@
         <v>26</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0745489076284746</v>
+        <v>0.0745232685650044</v>
       </c>
       <c r="D19"/>
     </row>
@@ -3616,7 +3616,7 @@
         <v>27</v>
       </c>
       <c r="C20" t="n">
-        <v>0.048049953067902</v>
+        <v>0.0480779483382211</v>
       </c>
       <c r="D20"/>
     </row>
@@ -3628,7 +3628,7 @@
         <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0447297899376656</v>
+        <v>0.0447144063464139</v>
       </c>
       <c r="D21"/>
     </row>
@@ -3640,7 +3640,7 @@
         <v>28</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0372744538142373</v>
+        <v>0.0372616342825022</v>
       </c>
       <c r="D22"/>
     </row>
@@ -3652,7 +3652,7 @@
         <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>0.034321713163202</v>
+        <v>0.0343410736648642</v>
       </c>
       <c r="D23"/>
     </row>
@@ -3664,7 +3664,7 @@
         <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>0.029819117690809</v>
+        <v>0.0298088622185905</v>
       </c>
       <c r="D24"/>
     </row>
@@ -3676,7 +3676,7 @@
         <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0205934732585021</v>
+        <v>0.0206041989915073</v>
       </c>
       <c r="D25"/>
     </row>
@@ -3688,7 +3688,7 @@
         <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0149106722468566</v>
+        <v>0.0149055441278233</v>
       </c>
       <c r="D26"/>
     </row>
@@ -3725,10 +3725,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>56.2950113123006</v>
+        <v>56.3041081219849</v>
       </c>
       <c r="D2" t="n">
-        <v>13.8490255669441</v>
+        <v>13.856182263946</v>
       </c>
     </row>
     <row r="3">
@@ -3739,10 +3739,10 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>17.0508572343531</v>
+        <v>17.0352886501756</v>
       </c>
       <c r="D3" t="n">
-        <v>4.68457221441722</v>
+        <v>4.67777158284229</v>
       </c>
     </row>
     <row r="4">
@@ -3753,10 +3753,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>8.97414045002143</v>
+        <v>8.97376302770651</v>
       </c>
       <c r="D4" t="n">
-        <v>2.23722456511995</v>
+        <v>2.23691437036538</v>
       </c>
     </row>
     <row r="5">
@@ -3767,10 +3767,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>4.65985259507985</v>
+        <v>4.66228845333324</v>
       </c>
       <c r="D5" t="n">
-        <v>3.20270178727532</v>
+        <v>3.20458350215252</v>
       </c>
     </row>
     <row r="6">
@@ -3781,10 +3781,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.95563362159775</v>
+        <v>2.95631754482207</v>
       </c>
       <c r="D6" t="n">
-        <v>0.166350486782069</v>
+        <v>0.166443705551338</v>
       </c>
     </row>
     <row r="7">
@@ -3795,10 +3795,10 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>2.06278940323585</v>
+        <v>2.06322419020452</v>
       </c>
       <c r="D7" t="n">
-        <v>0.443730531241504</v>
+        <v>0.443716737739581</v>
       </c>
     </row>
     <row r="8">
@@ -3809,10 +3809,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1.98068645471414</v>
+        <v>1.98260103785225</v>
       </c>
       <c r="D8" t="n">
-        <v>0.40990712214849</v>
+        <v>0.410246235998562</v>
       </c>
     </row>
     <row r="9">
@@ -3823,10 +3823,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.36113341054947</v>
+        <v>1.36142375061603</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0687858803288349</v>
+        <v>0.0688214454572211</v>
       </c>
     </row>
     <row r="10">
@@ -3837,10 +3837,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.967041921835672</v>
+        <v>0.967424695406141</v>
       </c>
       <c r="D10" t="n">
-        <v>0.137633057761389</v>
+        <v>0.137743280417042</v>
       </c>
     </row>
     <row r="11">
@@ -3851,10 +3851,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.783710097716881</v>
+        <v>0.783743056997747</v>
       </c>
       <c r="D11" t="n">
-        <v>0.064833146768481</v>
+        <v>0.0648284348756534</v>
       </c>
     </row>
     <row r="12">
@@ -3865,10 +3865,10 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>0.782625180169578</v>
+        <v>0.782826515834002</v>
       </c>
       <c r="D12" t="n">
-        <v>0.265920244800812</v>
+        <v>0.265934164649738</v>
       </c>
     </row>
     <row r="13">
@@ -3879,10 +3879,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>0.653944782403579</v>
+        <v>0.653790508001574</v>
       </c>
       <c r="D13" t="n">
-        <v>0.133944302900671</v>
+        <v>0.133970579529824</v>
       </c>
     </row>
     <row r="14">
@@ -3893,10 +3893,10 @@
         <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>0.42055134000046</v>
+        <v>0.420978721028352</v>
       </c>
       <c r="D14" t="n">
-        <v>0.251217866740883</v>
+        <v>0.251600768850808</v>
       </c>
     </row>
     <row r="15">
@@ -3907,10 +3907,10 @@
         <v>34</v>
       </c>
       <c r="C15" t="n">
-        <v>0.294797111390009</v>
+        <v>0.294801554152728</v>
       </c>
       <c r="D15" t="n">
-        <v>0.060127286461208</v>
+        <v>0.0601038972054638</v>
       </c>
     </row>
     <row r="16">
@@ -3921,7 +3921,7 @@
         <v>35</v>
       </c>
       <c r="C16" t="n">
-        <v>0.273245290917606</v>
+        <v>0.273220773321349</v>
       </c>
       <c r="D16"/>
     </row>
@@ -3933,10 +3933,10 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>0.110220518298119</v>
+        <v>0.110260935136766</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0450243073135336</v>
+        <v>0.0450239683206631</v>
       </c>
     </row>
     <row r="18">
@@ -3947,7 +3947,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0949843092504629</v>
+        <v>0.0948848870789554</v>
       </c>
       <c r="D18"/>
     </row>
@@ -3959,10 +3959,10 @@
         <v>31</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0905129096455505</v>
+        <v>0.0906268818335357</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0213347951269941</v>
+        <v>0.0213609609007617</v>
       </c>
     </row>
     <row r="20">
@@ -3973,7 +3973,7 @@
         <v>22</v>
       </c>
       <c r="C20" t="n">
-        <v>0.051722296985655</v>
+        <v>0.0517867896191633</v>
       </c>
       <c r="D20"/>
     </row>
@@ -3985,7 +3985,7 @@
         <v>37</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0374081938479166</v>
+        <v>0.0373818914578821</v>
       </c>
       <c r="D21"/>
     </row>
@@ -3997,10 +3997,10 @@
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>0.030170476513252</v>
+        <v>0.0302089606111786</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00304767836202143</v>
+        <v>0.00305156584296595</v>
       </c>
     </row>
     <row r="23">
@@ -4011,7 +4011,7 @@
         <v>38</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0215503403666086</v>
+        <v>0.0215778290079847</v>
       </c>
       <c r="D23"/>
     </row>
@@ -4023,7 +4023,7 @@
         <v>39</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0172402722932869</v>
+        <v>0.0172622632063878</v>
       </c>
       <c r="D24"/>
     </row>
@@ -4035,7 +4035,7 @@
         <v>17</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0172402722932869</v>
+        <v>0.0172622632063878</v>
       </c>
       <c r="D25"/>
     </row>
@@ -4047,7 +4047,7 @@
         <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0129302042199652</v>
+        <v>0.0129466974047908</v>
       </c>
       <c r="D26"/>
     </row>
@@ -4084,10 +4084,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>39.7281014519403</v>
+        <v>39.7290616830707</v>
       </c>
       <c r="D2" t="n">
-        <v>6.21860820764229</v>
+        <v>6.21835232915755</v>
       </c>
     </row>
     <row r="3">
@@ -4098,10 +4098,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>34.8879985888077</v>
+        <v>34.8859603682263</v>
       </c>
       <c r="D3" t="n">
-        <v>4.42073812416722</v>
+        <v>4.42043960561398</v>
       </c>
     </row>
     <row r="4">
@@ -4112,10 +4112,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>7.53251208659025</v>
+        <v>7.53238581525108</v>
       </c>
       <c r="D4" t="n">
-        <v>0.237454364070223</v>
+        <v>0.237447338734724</v>
       </c>
     </row>
     <row r="5">
@@ -4126,10 +4126,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>4.44575576170417</v>
+        <v>4.44623453436161</v>
       </c>
       <c r="D5" t="n">
-        <v>0.630523071027679</v>
+        <v>0.63055259443331</v>
       </c>
     </row>
     <row r="6">
@@ -4140,10 +4140,10 @@
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>3.87693343243817</v>
+        <v>3.87731620473622</v>
       </c>
       <c r="D6" t="n">
-        <v>0.911712337636597</v>
+        <v>0.911805512809434</v>
       </c>
     </row>
     <row r="7">
@@ -4154,10 +4154,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>3.25694228270683</v>
+        <v>3.25710668864576</v>
       </c>
       <c r="D7" t="n">
-        <v>0.70733559831466</v>
+        <v>0.707350658262006</v>
       </c>
     </row>
     <row r="8">
@@ -4168,10 +4168,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1.97872409787126</v>
+        <v>1.97872599818862</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1547972235296</v>
+        <v>0.154806328395301</v>
       </c>
     </row>
     <row r="9">
@@ -4182,7 +4182,7 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>1.12314048822747</v>
+        <v>1.12319999181149</v>
       </c>
       <c r="D9"/>
     </row>
@@ -4194,7 +4194,7 @@
         <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>0.918428526744664</v>
+        <v>0.918331540824173</v>
       </c>
       <c r="D10"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>0.558108885552207</v>
+        <v>0.558162676090998</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0461198226177086</v>
+        <v>0.0461237017220785</v>
       </c>
     </row>
     <row r="12">
@@ -4220,10 +4220,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>0.494833544322251</v>
+        <v>0.494917936870067</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0431730031535043</v>
+        <v>0.043185765399925</v>
       </c>
     </row>
     <row r="13">
@@ -4234,10 +4234,10 @@
         <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2535018465008</v>
+        <v>0.253525157028426</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0546702359334213</v>
+        <v>0.0546684509143556</v>
       </c>
     </row>
     <row r="14">
@@ -4248,10 +4248,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.149049513109839</v>
+        <v>0.149076724973757</v>
       </c>
       <c r="D14" t="n">
-        <v>0.022773446583883</v>
+        <v>0.0227812590279868</v>
       </c>
     </row>
     <row r="15">
@@ -4262,10 +4262,10 @@
         <v>31</v>
       </c>
       <c r="C15" t="n">
-        <v>0.108401006922979</v>
+        <v>0.108387807070915</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0395979660187865</v>
+        <v>0.0395979486402563</v>
       </c>
     </row>
     <row r="16">
@@ -4276,10 +4276,10 @@
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0983739961246108</v>
+        <v>0.0984050641522545</v>
       </c>
       <c r="D16" t="n">
-        <v>0.021972442960277</v>
+        <v>0.0219792946428027</v>
       </c>
     </row>
     <row r="17">
@@ -4290,10 +4290,10 @@
         <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0862854408888624</v>
+        <v>0.0863011193017688</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0119456540453731</v>
+        <v>0.0119485130265267</v>
       </c>
     </row>
     <row r="18">
@@ -4304,7 +4304,7 @@
         <v>35</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0846707889820255</v>
+        <v>0.0846647635257898</v>
       </c>
       <c r="D18"/>
     </row>
@@ -4316,7 +4316,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0603012976389215</v>
+        <v>0.0603064817301813</v>
       </c>
       <c r="D19"/>
     </row>
@@ -4328,7 +4328,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0567665798345247</v>
+        <v>0.056760670105872</v>
       </c>
       <c r="D20"/>
     </row>
@@ -4340,10 +4340,10 @@
         <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0500354950193752</v>
+        <v>0.0500356743516428</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0267642568796029</v>
+        <v>0.0267683469819272</v>
       </c>
     </row>
     <row r="22">
@@ -4354,10 +4354,10 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0376415257929039</v>
+        <v>0.0376593776481822</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0129554095710758</v>
+        <v>0.0129613740499146</v>
       </c>
     </row>
     <row r="23">
@@ -4368,10 +4368,10 @@
         <v>17</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0290869397978496</v>
+        <v>0.0291004962026295</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0157285794869354</v>
+        <v>0.0157351004563593</v>
       </c>
     </row>
     <row r="24">
@@ -4382,10 +4382,10 @@
         <v>44</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0268330144888622</v>
+        <v>0.0268281539567913</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00748556523992058</v>
+        <v>0.00748741271841554</v>
       </c>
     </row>
     <row r="25">
@@ -4396,7 +4396,7 @@
         <v>45</v>
       </c>
       <c r="C25" t="n">
-        <v>0.026401093232374</v>
+        <v>0.0263889491829003</v>
       </c>
       <c r="D25"/>
     </row>
@@ -4408,7 +4408,7 @@
         <v>46</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0222428218635845</v>
+        <v>0.0222527924706864</v>
       </c>
       <c r="D26"/>
     </row>
@@ -4420,7 +4420,7 @@
         <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>0.016358362596248</v>
+        <v>0.0163605648822847</v>
       </c>
       <c r="D27"/>
     </row>
@@ -4432,7 +4432,7 @@
         <v>28</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0162468266045379</v>
+        <v>0.0162393533433233</v>
       </c>
       <c r="D28"/>
     </row>
@@ -4444,7 +4444,7 @@
         <v>39</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0142159732789706</v>
+        <v>0.0142094341754078</v>
       </c>
       <c r="D29"/>
     </row>
@@ -4456,7 +4456,7 @@
         <v>38</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0121851199534034</v>
+        <v>0.0121795150074924</v>
       </c>
       <c r="D30"/>
     </row>
@@ -4468,7 +4468,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0121851199534034</v>
+        <v>0.0121795150074924</v>
       </c>
       <c r="D31"/>
     </row>
@@ -4480,7 +4480,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00812341330226893</v>
+        <v>0.00811967667166163</v>
       </c>
       <c r="D32"/>
     </row>
@@ -4492,7 +4492,7 @@
         <v>48</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00812341330226893</v>
+        <v>0.00811967667166163</v>
       </c>
       <c r="D33"/>
     </row>
@@ -4504,7 +4504,7 @@
         <v>25</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0068441179342651</v>
+        <v>0.00684695551256686</v>
       </c>
       <c r="D34"/>
     </row>
@@ -4516,7 +4516,7 @@
         <v>49</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0060925599767017</v>
+        <v>0.00608975750374622</v>
       </c>
       <c r="D35"/>
     </row>
@@ -4528,7 +4528,7 @@
         <v>15</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00513290130977313</v>
+        <v>0.00513502957958107</v>
       </c>
       <c r="D36"/>
     </row>
@@ -4540,7 +4540,7 @@
         <v>50</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00342168468528117</v>
+        <v>0.00342385186597158</v>
       </c>
       <c r="D37"/>
     </row>
@@ -5074,10 +5074,10 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>15.9046629771807</v>
+        <v>15.9133360695454</v>
       </c>
       <c r="D2" t="n">
-        <v>1.08475902120531</v>
+        <v>1.0856805763707</v>
       </c>
     </row>
     <row r="3">
@@ -5088,10 +5088,10 @@
         <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>11.4997988322463</v>
+        <v>11.4962127695466</v>
       </c>
       <c r="D3" t="n">
-        <v>1.83502063905079</v>
+        <v>1.8347445177039</v>
       </c>
     </row>
     <row r="4">
@@ -5102,10 +5102,10 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>11.2813693050418</v>
+        <v>11.2805137349966</v>
       </c>
       <c r="D4" t="n">
-        <v>0.902135180565654</v>
+        <v>0.901845088166167</v>
       </c>
     </row>
     <row r="5">
@@ -5116,10 +5116,10 @@
         <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>9.04064253626956</v>
+        <v>9.04007656688433</v>
       </c>
       <c r="D5" t="n">
-        <v>1.22878413366926</v>
+        <v>1.22890237664976</v>
       </c>
     </row>
     <row r="6">
@@ -5130,10 +5130,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>8.11880458079717</v>
+        <v>8.1187833078828</v>
       </c>
       <c r="D6" t="n">
-        <v>0.597163209200319</v>
+        <v>0.597374451018991</v>
       </c>
     </row>
     <row r="7">
@@ -5144,10 +5144,10 @@
         <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>7.26546809884088</v>
+        <v>7.26449224855581</v>
       </c>
       <c r="D7" t="n">
-        <v>0.509778166469935</v>
+        <v>0.509542697259636</v>
       </c>
     </row>
     <row r="8">
@@ -5158,10 +5158,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>5.88840392521765</v>
+        <v>5.88727823712654</v>
       </c>
       <c r="D8" t="n">
-        <v>0.590100815130695</v>
+        <v>0.590136456318376</v>
       </c>
     </row>
     <row r="9">
@@ -5172,10 +5172,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>4.44997202434239</v>
+        <v>4.44837417124006</v>
       </c>
       <c r="D9" t="n">
-        <v>0.965439863915427</v>
+        <v>0.965417078288699</v>
       </c>
     </row>
     <row r="10">
@@ -5186,10 +5186,10 @@
         <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>3.50914346504936</v>
+        <v>3.50962344380878</v>
       </c>
       <c r="D10" t="n">
-        <v>0.207091168383744</v>
+        <v>0.207271608753574</v>
       </c>
     </row>
     <row r="11">
@@ -5200,10 +5200,10 @@
         <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>3.43804653531843</v>
+        <v>3.43986679846598</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0946539325824996</v>
+        <v>0.0947048533378927</v>
       </c>
     </row>
     <row r="12">
@@ -5214,10 +5214,10 @@
         <v>57</v>
       </c>
       <c r="C12" t="n">
-        <v>2.64075687429571</v>
+        <v>2.6415769192628</v>
       </c>
       <c r="D12" t="n">
-        <v>0.595101776309266</v>
+        <v>0.595357459589207</v>
       </c>
     </row>
     <row r="13">
@@ -5228,10 +5228,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>2.43688047244979</v>
+        <v>2.43792174692203</v>
       </c>
       <c r="D13" t="n">
-        <v>0.244277250081718</v>
+        <v>0.244464437518885</v>
       </c>
     </row>
     <row r="14">
@@ -5242,10 +5242,10 @@
         <v>59</v>
       </c>
       <c r="C14" t="n">
-        <v>1.84799400726404</v>
+        <v>1.84783337527055</v>
       </c>
       <c r="D14" t="n">
-        <v>0.249230689888784</v>
+        <v>0.249197462551498</v>
       </c>
     </row>
     <row r="15">
@@ -5256,10 +5256,10 @@
         <v>56</v>
       </c>
       <c r="C15" t="n">
-        <v>1.66033677490238</v>
+        <v>1.6606175322496</v>
       </c>
       <c r="D15" t="n">
-        <v>1.13579060248245</v>
+        <v>1.13593148240188</v>
       </c>
     </row>
     <row r="16">
@@ -5270,10 +5270,10 @@
         <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>1.31606078298467</v>
+        <v>1.31604890737969</v>
       </c>
       <c r="D16" t="n">
-        <v>0.361395917771337</v>
+        <v>0.36116100920028</v>
       </c>
     </row>
     <row r="17">
@@ -5284,10 +5284,10 @@
         <v>71</v>
       </c>
       <c r="C17" t="n">
-        <v>1.25747421750289</v>
+        <v>1.25638189709843</v>
       </c>
       <c r="D17" t="n">
-        <v>0.253631704218556</v>
+        <v>0.254132630138318</v>
       </c>
     </row>
     <row r="18">
@@ -5298,10 +5298,10 @@
         <v>65</v>
       </c>
       <c r="C18" t="n">
-        <v>1.07670400831027</v>
+        <v>1.07711794991603</v>
       </c>
       <c r="D18" t="n">
-        <v>0.298241259617882</v>
+        <v>0.298351762732855</v>
       </c>
     </row>
     <row r="19">
@@ -5312,10 +5312,10 @@
         <v>62</v>
       </c>
       <c r="C19" t="n">
-        <v>0.87912479341694</v>
+        <v>0.879560142730045</v>
       </c>
       <c r="D19" t="n">
-        <v>0.14776043556623</v>
+        <v>0.147758199768971</v>
       </c>
     </row>
     <row r="20">
@@ -5326,10 +5326,10 @@
         <v>45</v>
       </c>
       <c r="C20" t="n">
-        <v>0.826099667163471</v>
+        <v>0.824933538631586</v>
       </c>
       <c r="D20" t="n">
-        <v>0.172201923099766</v>
+        <v>0.171922117135325</v>
       </c>
     </row>
     <row r="21">
@@ -5340,10 +5340,10 @@
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>0.74281337850058</v>
+        <v>0.741563473474212</v>
       </c>
       <c r="D21" t="n">
-        <v>0.49049152785471</v>
+        <v>0.489687992578949</v>
       </c>
     </row>
     <row r="22">
@@ -5354,10 +5354,10 @@
         <v>60</v>
       </c>
       <c r="C22" t="n">
-        <v>0.693226457958619</v>
+        <v>0.692893953665318</v>
       </c>
       <c r="D22" t="n">
-        <v>0.32670105585919</v>
+        <v>0.326398657182892</v>
       </c>
     </row>
     <row r="23">
@@ -5368,10 +5368,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="n">
-        <v>0.547062921171909</v>
+        <v>0.547646792897094</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0909057071915145</v>
+        <v>0.0909623774484016</v>
       </c>
     </row>
     <row r="24">
@@ -5382,10 +5382,10 @@
         <v>64</v>
       </c>
       <c r="C24" t="n">
-        <v>0.419796251115969</v>
+        <v>0.419715937423794</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0794751912347708</v>
+        <v>0.0793898603845195</v>
       </c>
     </row>
     <row r="25">
@@ -5396,10 +5396,10 @@
         <v>70</v>
       </c>
       <c r="C25" t="n">
-        <v>0.408857309590412</v>
+        <v>0.408906370374657</v>
       </c>
       <c r="D25" t="n">
-        <v>0.089609232738448</v>
+        <v>0.0895754778806432</v>
       </c>
     </row>
     <row r="26">
@@ -5410,10 +5410,10 @@
         <v>68</v>
       </c>
       <c r="C26" t="n">
-        <v>0.359219098942673</v>
+        <v>0.359167539819473</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0238016846565754</v>
+        <v>0.0237482075559623</v>
       </c>
     </row>
     <row r="27">
@@ -5424,10 +5424,10 @@
         <v>61</v>
       </c>
       <c r="C27" t="n">
-        <v>0.312281577657832</v>
+        <v>0.312328729415327</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0582763759092555</v>
+        <v>0.0580625396139329</v>
       </c>
     </row>
     <row r="28">
@@ -5438,10 +5438,10 @@
         <v>21</v>
       </c>
       <c r="C28" t="n">
-        <v>0.298005242007987</v>
+        <v>0.297697170490835</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0245469511332483</v>
+        <v>0.0245026224151622</v>
       </c>
     </row>
     <row r="29">
@@ -5452,7 +5452,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="n">
-        <v>0.251395800537696</v>
+        <v>0.251333021127533</v>
       </c>
       <c r="D29"/>
     </row>
@@ -5464,7 +5464,7 @@
         <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>0.219769260139959</v>
+        <v>0.219623369698133</v>
       </c>
       <c r="D30"/>
     </row>
@@ -5476,10 +5476,10 @@
         <v>63</v>
       </c>
       <c r="C31" t="n">
-        <v>0.21788302228434</v>
+        <v>0.217897650374912</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0871378672283708</v>
+        <v>0.0870470200100146</v>
       </c>
     </row>
     <row r="32">
@@ -5490,7 +5490,7 @@
         <v>13</v>
       </c>
       <c r="C32" t="n">
-        <v>0.206343632796305</v>
+        <v>0.206220812316201</v>
       </c>
       <c r="D32"/>
     </row>
@@ -5502,10 +5502,10 @@
         <v>74</v>
       </c>
       <c r="C33" t="n">
-        <v>0.138580559940982</v>
+        <v>0.138286935951815</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0884303688003574</v>
+        <v>0.0882073973999568</v>
       </c>
     </row>
     <row r="34">
@@ -5516,10 +5516,10 @@
         <v>72</v>
       </c>
       <c r="C34" t="n">
-        <v>0.127680528150844</v>
+        <v>0.127532069617423</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0239303508272499</v>
+        <v>0.0239786372902238</v>
       </c>
     </row>
     <row r="35">
@@ -5530,7 +5530,7 @@
         <v>75</v>
       </c>
       <c r="C35" t="n">
-        <v>0.114468904351991</v>
+        <v>0.114437424323326</v>
       </c>
       <c r="D35"/>
     </row>
@@ -5542,10 +5542,10 @@
         <v>48</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0850947070476735</v>
+        <v>0.0849846185119218</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0283005944105174</v>
+        <v>0.0281740877995576</v>
       </c>
     </row>
     <row r="37">
@@ -5556,7 +5556,7 @@
         <v>76</v>
       </c>
       <c r="C37" t="n">
-        <v>0.083112079165677</v>
+        <v>0.083118618323469</v>
       </c>
       <c r="D37"/>
     </row>
@@ -5568,10 +5568,10 @@
         <v>77</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0826672701448722</v>
+        <v>0.0824763260600204</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00157951570916209</v>
+        <v>0.00157586735859885</v>
       </c>
     </row>
     <row r="39">
@@ -5582,7 +5582,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>0.081013606389594</v>
+        <v>0.0810849869124129</v>
       </c>
       <c r="D39"/>
     </row>
@@ -5594,10 +5594,10 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0625588957431237</v>
+        <v>0.0624143977927732</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00844884085840169</v>
+        <v>0.00842932580506875</v>
       </c>
     </row>
     <row r="41">
@@ -5608,10 +5608,10 @@
         <v>8</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0491536075793476</v>
+        <v>0.049040073037806</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0123053091295971</v>
+        <v>0.0122768864420395</v>
       </c>
     </row>
     <row r="42">
@@ -5622,10 +5622,10 @@
         <v>78</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0447621133500903</v>
+        <v>0.044693130754824</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0189029136531948</v>
+        <v>0.0188349213869587</v>
       </c>
     </row>
     <row r="43">
@@ -5636,10 +5636,10 @@
         <v>32</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0268689409306797</v>
+        <v>0.0268333473908288</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00943832546084426</v>
+        <v>0.00939780914090776</v>
       </c>
     </row>
     <row r="44">
@@ -5650,10 +5650,10 @@
         <v>10</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0245768037896738</v>
+        <v>0.024520036518903</v>
       </c>
       <c r="D44" t="n">
-        <v>0.011059111176659</v>
+        <v>0.0110335669454391</v>
       </c>
     </row>
     <row r="45">
@@ -5664,10 +5664,10 @@
         <v>19</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0224394212781726</v>
+        <v>0.02243082212351</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0000681580412900505</v>
+        <v>0.0000985696922639011</v>
       </c>
     </row>
     <row r="46">
@@ -5678,7 +5678,7 @@
         <v>28</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0178737175517015</v>
+        <v>0.017832433006623</v>
       </c>
       <c r="D46"/>
     </row>
@@ -5690,7 +5690,7 @@
         <v>36</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0157752447756186</v>
+        <v>0.0157988015955669</v>
       </c>
       <c r="D47"/>
     </row>
@@ -5702,7 +5702,7 @@
         <v>17</v>
       </c>
       <c r="C48" t="n">
-        <v>0.00450733912334368</v>
+        <v>0.00451369123599265</v>
       </c>
       <c r="D48"/>
     </row>
@@ -5714,7 +5714,7 @@
         <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>0.00446842938792537</v>
+        <v>0.00445810825165575</v>
       </c>
       <c r="D49"/>
     </row>
@@ -5751,10 +5751,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>57.3281405082253</v>
+        <v>57.3281477801791</v>
       </c>
       <c r="D2" t="n">
-        <v>40.3536957324513</v>
+        <v>40.3536922096008</v>
       </c>
     </row>
     <row r="3">
@@ -5765,7 +5765,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>31.1608311737856</v>
+        <v>31.1608281680983</v>
       </c>
       <c r="D3"/>
     </row>
@@ -5777,7 +5777,7 @@
         <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>8.10635960191601</v>
+        <v>8.10635394396169</v>
       </c>
       <c r="D4"/>
     </row>
@@ -5789,7 +5789,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>2.98313940681246</v>
+        <v>2.98314090517806</v>
       </c>
       <c r="D5"/>
     </row>
@@ -5801,7 +5801,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>0.42152930926069</v>
+        <v>0.421529202582811</v>
       </c>
       <c r="D6"/>
     </row>
@@ -5838,10 +5838,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>94.0187702741291</v>
+        <v>94.0396963929599</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8363407254187</v>
+        <v>29.8417603709548</v>
       </c>
     </row>
     <row r="3">
@@ -5852,10 +5852,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>2.46890703144531</v>
+        <v>2.46278487288434</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08710525321409</v>
+        <v>0.0870575126095609</v>
       </c>
     </row>
     <row r="4">
@@ -5866,10 +5866,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>0.760679645127287</v>
+        <v>0.759402820259848</v>
       </c>
       <c r="D4" t="n">
-        <v>0.116497598478017</v>
+        <v>0.116513645389048</v>
       </c>
     </row>
     <row r="5">
@@ -5880,10 +5880,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>0.570724366816388</v>
+        <v>0.567713398141494</v>
       </c>
       <c r="D5" t="n">
-        <v>0.388472017279955</v>
+        <v>0.386431784779191</v>
       </c>
     </row>
     <row r="6">
@@ -5894,10 +5894,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>0.425316442856433</v>
+        <v>0.422812373434628</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0199609849779236</v>
+        <v>0.0198434714759365</v>
       </c>
     </row>
     <row r="7">
@@ -5908,7 +5908,7 @@
         <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>0.362943249913339</v>
+        <v>0.362226789991755</v>
       </c>
       <c r="D7"/>
     </row>
@@ -5920,10 +5920,10 @@
         <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>0.237303217074989</v>
+        <v>0.23590627630397</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0202267483024398</v>
+        <v>0.0201076901838695</v>
       </c>
     </row>
     <row r="9">
@@ -5934,10 +5934,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>0.199192433748206</v>
+        <v>0.198019888344106</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0222951020193061</v>
+        <v>0.0221638051926366</v>
       </c>
     </row>
     <row r="10">
@@ -5948,10 +5948,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.190898338682771</v>
+        <v>0.190677332152804</v>
       </c>
       <c r="D10" t="n">
-        <v>0.064368226732903</v>
+        <v>0.0644377307378925</v>
       </c>
     </row>
     <row r="11">
@@ -5962,10 +5962,10 @@
         <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>0.142788171635953</v>
+        <v>0.141947808790897</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0318242838983415</v>
+        <v>0.0316369585666598</v>
       </c>
     </row>
     <row r="12">
@@ -5976,10 +5976,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>0.105694253405797</v>
+        <v>0.105071841369835</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00655903092408336</v>
+        <v>0.00652037608813461</v>
       </c>
     </row>
     <row r="13">
@@ -5990,10 +5990,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0818111706369464</v>
+        <v>0.0813294628481086</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0110361643657286</v>
+        <v>0.0109712459676748</v>
       </c>
     </row>
     <row r="14">
@@ -6004,10 +6004,10 @@
         <v>53</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0660585929738167</v>
+        <v>0.0656698226017681</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0127913561117006</v>
+        <v>0.0127160107463229</v>
       </c>
     </row>
     <row r="15">
@@ -6018,10 +6018,10 @@
         <v>25</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0518306821460141</v>
+        <v>0.0515256044852872</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0107792383840783</v>
+        <v>0.0107159477595823</v>
       </c>
     </row>
     <row r="16">
@@ -6032,10 +6032,10 @@
         <v>45</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0299804884909323</v>
+        <v>0.0298040670411648</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00826426118102878</v>
+        <v>0.00821557962339601</v>
       </c>
     </row>
     <row r="17">
@@ -6046,10 +6046,10 @@
         <v>55</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0243908845075512</v>
+        <v>0.024247380112784</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00221492775885409</v>
+        <v>0.00220192113925494</v>
       </c>
     </row>
     <row r="18">
@@ -6060,10 +6060,10 @@
         <v>81</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02388287249898</v>
+        <v>0.023742169843383</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00467103303641761</v>
+        <v>0.00464364622282581</v>
       </c>
     </row>
     <row r="19">
@@ -6074,10 +6074,10 @@
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0213419713766395</v>
+        <v>0.0212165358530648</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00881592715433516</v>
+        <v>0.00876410834067219</v>
       </c>
     </row>
     <row r="20">
@@ -6088,10 +6088,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0208339593680683</v>
+        <v>0.0207113255836637</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0057113585077658</v>
+        <v>0.00567783010644786</v>
       </c>
     </row>
     <row r="21">
@@ -6102,10 +6102,10 @@
         <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>0.020325737089626</v>
+        <v>0.0202061153142627</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0071863076059706</v>
+        <v>0.00714401435901212</v>
       </c>
     </row>
     <row r="22">
@@ -6116,7 +6116,7 @@
         <v>62</v>
       </c>
       <c r="C22" t="n">
-        <v>0.018293268515599</v>
+        <v>0.0181854829150021</v>
       </c>
       <c r="D22"/>
     </row>
@@ -6128,7 +6128,7 @@
         <v>70</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0177850462371566</v>
+        <v>0.0176802726456011</v>
       </c>
       <c r="D23"/>
     </row>
@@ -6140,7 +6140,7 @@
         <v>71</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0142281210976738</v>
+        <v>0.0141442181164809</v>
       </c>
       <c r="D24"/>
     </row>
@@ -6152,7 +6152,7 @@
         <v>52</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0137198988192314</v>
+        <v>0.0136390078470799</v>
       </c>
       <c r="D25"/>
     </row>
@@ -6164,7 +6164,7 @@
         <v>54</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0127036645322179</v>
+        <v>0.0126287959866213</v>
       </c>
       <c r="D26"/>
     </row>
@@ -6176,7 +6176,7 @@
         <v>82</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0121954422537756</v>
+        <v>0.0121235857172203</v>
       </c>
       <c r="D27"/>
     </row>
@@ -6188,7 +6188,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0116872199753333</v>
+        <v>0.0116185841261627</v>
       </c>
       <c r="D28"/>
     </row>
@@ -6200,10 +6200,10 @@
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0106709856883198</v>
+        <v>0.0106083722657041</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00176029081686764</v>
+        <v>0.00174985874922072</v>
       </c>
     </row>
     <row r="30">
@@ -6214,7 +6214,7 @@
         <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00965475140130624</v>
+        <v>0.00959795172690207</v>
       </c>
       <c r="D30"/>
     </row>
@@ -6223,26 +6223,26 @@
         <v>80</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00762228282727919</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.00107795357505818</v>
-      </c>
+        <v>0.00757731932764146</v>
+      </c>
+      <c r="D31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
         <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00762207255740809</v>
-      </c>
-      <c r="D32"/>
+        <v>0.00757711064929804</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.00107156526438389</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
@@ -6252,7 +6252,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="D33"/>
     </row>
@@ -6264,7 +6264,7 @@
         <v>83</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="D34"/>
     </row>
@@ -6276,7 +6276,7 @@
         <v>64</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00660583827039457</v>
+        <v>0.00656689878883944</v>
       </c>
       <c r="D35"/>
     </row>
@@ -6288,7 +6288,7 @@
         <v>42</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00609782626182335</v>
+        <v>0.00606189719778185</v>
       </c>
       <c r="D36"/>
     </row>
@@ -6300,7 +6300,7 @@
         <v>63</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00508138170493873</v>
+        <v>0.00505147665897983</v>
       </c>
       <c r="D37"/>
     </row>
@@ -6312,7 +6312,7 @@
         <v>58</v>
       </c>
       <c r="C38" t="n">
-        <v>0.00355692513948289</v>
+        <v>0.00353605452912022</v>
       </c>
       <c r="D38"/>
     </row>
@@ -6324,7 +6324,7 @@
         <v>39</v>
       </c>
       <c r="C39" t="n">
-        <v>0.00254069085246936</v>
+        <v>0.00252584266866162</v>
       </c>
       <c r="D39"/>
     </row>
@@ -6336,7 +6336,7 @@
         <v>84</v>
       </c>
       <c r="C40" t="n">
-        <v>0.00203267884389815</v>
+        <v>0.00202063239926062</v>
       </c>
       <c r="D40"/>
     </row>
@@ -6373,10 +6373,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>25.1964424022149</v>
+        <v>25.1965367592767</v>
       </c>
       <c r="D2" t="n">
-        <v>1.93523792598481</v>
+        <v>1.93543404111971</v>
       </c>
     </row>
     <row r="3">
@@ -6387,10 +6387,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>18.1689234804074</v>
+        <v>18.1673264885753</v>
       </c>
       <c r="D3" t="n">
-        <v>0.432739320612276</v>
+        <v>0.432718841054423</v>
       </c>
     </row>
     <row r="4">
@@ -6401,10 +6401,10 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>11.2867641756239</v>
+        <v>11.2870459326145</v>
       </c>
       <c r="D4" t="n">
-        <v>7.79747841092047</v>
+        <v>7.79773733744146</v>
       </c>
     </row>
     <row r="5">
@@ -6415,10 +6415,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>8.0097858428954</v>
+        <v>8.01115393796449</v>
       </c>
       <c r="D5" t="n">
-        <v>1.60905995460106</v>
+        <v>1.60936124402573</v>
       </c>
     </row>
     <row r="6">
@@ -6429,10 +6429,10 @@
         <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>6.77989306604406</v>
+        <v>6.77881974051897</v>
       </c>
       <c r="D6" t="n">
-        <v>1.16354430973066</v>
+        <v>1.16335433995446</v>
       </c>
     </row>
     <row r="7">
@@ -6443,10 +6443,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>4.87573278327654</v>
+        <v>4.87725512036695</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0993527028685948</v>
+        <v>0.099401333768649</v>
       </c>
     </row>
     <row r="8">
@@ -6457,10 +6457,10 @@
         <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>4.36324664897001</v>
+        <v>4.36332007175648</v>
       </c>
       <c r="D8" t="n">
-        <v>0.534854245506558</v>
+        <v>0.534909041154877</v>
       </c>
     </row>
     <row r="9">
@@ -6471,10 +6471,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>4.17942439810022</v>
+        <v>4.17865556908465</v>
       </c>
       <c r="D9" t="n">
-        <v>0.629474802709262</v>
+        <v>0.629336454614041</v>
       </c>
     </row>
     <row r="10">
@@ -6485,10 +6485,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2.7812086367447</v>
+        <v>2.78086546106678</v>
       </c>
       <c r="D10" t="n">
-        <v>0.241037391606985</v>
+        <v>0.240987580928254</v>
       </c>
     </row>
     <row r="11">
@@ -6499,10 +6499,10 @@
         <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>2.65381557600859</v>
+        <v>2.65389443500849</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10004303459688</v>
+        <v>1.1000766666257</v>
       </c>
     </row>
     <row r="12">
@@ -6513,10 +6513,10 @@
         <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>1.75956025425825</v>
+        <v>1.75958608100551</v>
       </c>
       <c r="D12" t="n">
-        <v>0.115464162238769</v>
+        <v>0.115450531966808</v>
       </c>
     </row>
     <row r="13">
@@ -6527,10 +6527,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>1.63554415932806</v>
+        <v>1.63559752828711</v>
       </c>
       <c r="D13" t="n">
-        <v>0.122376670856706</v>
+        <v>0.122374919760594</v>
       </c>
     </row>
     <row r="14">
@@ -6541,10 +6541,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>1.54503415439421</v>
+        <v>1.54499986880777</v>
       </c>
       <c r="D14" t="n">
-        <v>0.250650727927502</v>
+        <v>0.250653674269885</v>
       </c>
     </row>
     <row r="15">
@@ -6555,10 +6555,10 @@
         <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0631987894026</v>
+        <v>1.06308706922884</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0927383291354896</v>
+        <v>0.0927261331216983</v>
       </c>
     </row>
     <row r="16">
@@ -6569,10 +6569,10 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>0.897465727183185</v>
+        <v>0.897466482214415</v>
       </c>
       <c r="D16" t="n">
-        <v>0.461719332595731</v>
+        <v>0.461701075394256</v>
       </c>
     </row>
     <row r="17">
@@ -6583,10 +6583,10 @@
         <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>0.57047476881237</v>
+        <v>0.570547149921031</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0747425037899925</v>
+        <v>0.0747481597976273</v>
       </c>
     </row>
     <row r="18">
@@ -6597,10 +6597,10 @@
         <v>38</v>
       </c>
       <c r="C18" t="n">
-        <v>0.541242508169327</v>
+        <v>0.541432354961316</v>
       </c>
       <c r="D18" t="n">
-        <v>0.237512932641943</v>
+        <v>0.237616433436933</v>
       </c>
     </row>
     <row r="19">
@@ -6611,10 +6611,10 @@
         <v>81</v>
       </c>
       <c r="C19" t="n">
-        <v>0.524260671449889</v>
+        <v>0.524152306972405</v>
       </c>
       <c r="D19" t="n">
-        <v>0.323530587624025</v>
+        <v>0.323469312291106</v>
       </c>
     </row>
     <row r="20">
@@ -6625,10 +6625,10 @@
         <v>25</v>
       </c>
       <c r="C20" t="n">
-        <v>0.437457092400592</v>
+        <v>0.437680707236282</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0974223302537888</v>
+        <v>0.0974726660697121</v>
       </c>
     </row>
     <row r="21">
@@ -6639,10 +6639,10 @@
         <v>35</v>
       </c>
       <c r="C21" t="n">
-        <v>0.297590307020918</v>
+        <v>0.297553863194058</v>
       </c>
       <c r="D21" t="n">
-        <v>0.105589392066944</v>
+        <v>0.105597733144794</v>
       </c>
     </row>
     <row r="22">
@@ -6653,10 +6653,10 @@
         <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>0.25487580782696</v>
+        <v>0.254814837259604</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0191447711243624</v>
+        <v>0.0191428227718087</v>
       </c>
     </row>
     <row r="23">
@@ -6667,7 +6667,7 @@
         <v>42</v>
       </c>
       <c r="C23" t="n">
-        <v>0.253991756615979</v>
+        <v>0.253949371069562</v>
       </c>
       <c r="D23"/>
     </row>
@@ -6679,7 +6679,7 @@
         <v>86</v>
       </c>
       <c r="C24" t="n">
-        <v>0.181624020011844</v>
+        <v>0.181564926084247</v>
       </c>
       <c r="D24"/>
     </row>
@@ -6691,10 +6691,10 @@
         <v>37</v>
       </c>
       <c r="C25" t="n">
-        <v>0.173577872758271</v>
+        <v>0.173568969952148</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0241654040245121</v>
+        <v>0.0241653376278085</v>
       </c>
     </row>
     <row r="26">
@@ -6705,7 +6705,7 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.16432736588394</v>
+        <v>0.164414789510755</v>
       </c>
       <c r="D26"/>
     </row>
@@ -6717,10 +6717,10 @@
         <v>67</v>
       </c>
       <c r="C27" t="n">
-        <v>0.156667419055868</v>
+        <v>0.156728059142117</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0238887665894522</v>
+        <v>0.0238873408762922</v>
       </c>
     </row>
     <row r="28">
@@ -6731,7 +6731,7 @@
         <v>53</v>
       </c>
       <c r="C28" t="n">
-        <v>0.137005973696932</v>
+        <v>0.137063862219539</v>
       </c>
       <c r="D28"/>
     </row>
@@ -6743,10 +6743,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="n">
-        <v>0.125886696043279</v>
+        <v>0.12594820237915</v>
       </c>
       <c r="D29" t="n">
-        <v>0.010537225521728</v>
+        <v>0.0105463945417804</v>
       </c>
     </row>
     <row r="30">
@@ -6757,7 +6757,7 @@
         <v>71</v>
       </c>
       <c r="C30" t="n">
-        <v>0.122247992508224</v>
+        <v>0.122261279814807</v>
       </c>
       <c r="D30"/>
     </row>
@@ -6766,26 +6766,26 @@
         <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="C31" t="n">
-        <v>0.11370582480294</v>
-      </c>
-      <c r="D31"/>
+        <v>0.113714572470864</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0203644825135999</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
         <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="C32" t="n">
-        <v>0.11370582480294</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.020369505421689</v>
-      </c>
+        <v>0.113712742732618</v>
+      </c>
+      <c r="D32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
@@ -6795,10 +6795,10 @@
         <v>55</v>
       </c>
       <c r="C33" t="n">
-        <v>0.108551604906202</v>
+        <v>0.108576667477973</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0205206678670958</v>
+        <v>0.0205241840114384</v>
       </c>
     </row>
     <row r="34">
@@ -6809,7 +6809,7 @@
         <v>48</v>
       </c>
       <c r="C34" t="n">
-        <v>0.107491841653286</v>
+        <v>0.10745686767183</v>
       </c>
       <c r="D34"/>
     </row>
@@ -6821,10 +6821,10 @@
         <v>15</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0971852321935793</v>
+        <v>0.0971847171625386</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0203933620660771</v>
+        <v>0.0203647318536465</v>
       </c>
     </row>
     <row r="36">
@@ -6835,7 +6835,7 @@
         <v>87</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0741321783585579</v>
+        <v>0.0741080584124175</v>
       </c>
       <c r="D36"/>
     </row>
@@ -6847,7 +6847,7 @@
         <v>39</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0381954051154606</v>
+        <v>0.0381921263948049</v>
       </c>
       <c r="D37"/>
     </row>
@@ -6859,10 +6859,10 @@
         <v>65</v>
       </c>
       <c r="C38" t="n">
-        <v>0.037313184238249</v>
+        <v>0.0373284899430084</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0159010500948038</v>
+        <v>0.0159152837694857</v>
       </c>
     </row>
     <row r="39">
@@ -6873,7 +6873,7 @@
         <v>22</v>
       </c>
       <c r="C39" t="n">
-        <v>0.037066089179279</v>
+        <v>0.0370540292062087</v>
       </c>
       <c r="D39"/>
     </row>
@@ -6885,7 +6885,7 @@
         <v>59</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0296532374101772</v>
+        <v>0.029643589312616</v>
       </c>
       <c r="D40"/>
     </row>
@@ -6897,7 +6897,7 @@
         <v>12</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0222403856410754</v>
+        <v>0.0222331494190234</v>
       </c>
       <c r="D41"/>
     </row>
@@ -6909,7 +6909,7 @@
         <v>28</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0222403856410754</v>
+        <v>0.0222331494190234</v>
       </c>
       <c r="D42"/>
     </row>
@@ -6921,7 +6921,7 @@
         <v>88</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0213581647638638</v>
+        <v>0.0213713427054722</v>
       </c>
       <c r="D43"/>
     </row>
@@ -6933,7 +6933,7 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0185339597565246</v>
+        <v>0.018527929472227</v>
       </c>
       <c r="D44"/>
     </row>
@@ -6945,7 +6945,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0128141667248102</v>
+        <v>0.0128228056232833</v>
       </c>
       <c r="D45"/>
     </row>
@@ -6957,7 +6957,7 @@
         <v>90</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00854216770528344</v>
+        <v>0.00854853708218889</v>
       </c>
       <c r="D46"/>
     </row>
